--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/feb-2025.xlsx
@@ -562,7 +562,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1728,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1854,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1919,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1984,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2240,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2305,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2370,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2496,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2561,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2687,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2752,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2817,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2882,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2947,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3012,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3077,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3142,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3207,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3272,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3337,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3402,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3467,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3532,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3658,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3723,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3788,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3853,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3918,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3983,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4048,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4113,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4243,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4430,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4495,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4560,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4625,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4690,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4755,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4820,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4885,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4950,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +5015,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5080,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5145,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5210,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5275,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5340,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5405,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5470,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5535,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5600,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5665,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5730,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5795,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5860,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5925,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5990,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6055,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6120,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6185,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6250,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6315,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6380,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6567,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6632,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6697,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6884,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +7010,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7075,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7140,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7205,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7270,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7396,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7461,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7526,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7591,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7656,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7721,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7786,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7851,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7916,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7981,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +8046,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8111,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8176,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8241,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8306,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8371,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8497,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8623,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8688,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8814,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8879,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +9005,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +9070,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9196,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9261,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9326,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9391,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9517,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9643,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9708,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9773,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9838,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9903,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9968,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10094,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10159,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
